--- a/students.xlsx
+++ b/students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$I$16</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -255,6 +255,145 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Student Marks</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Students'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Students'!$A$2:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Students'!$D$2:$D$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Students</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Marks</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -580,7 +719,7 @@
       </c>
       <c r="H1" s="8" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>Dynamic Statistics</t>
         </is>
       </c>
     </row>
@@ -837,8 +976,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F16"/>
+  <autoFilter ref="A1:I16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/students.xlsx
+++ b/students.xlsx
@@ -369,6 +369,348 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Student Marks</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Students'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Students'!$A$2:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Students'!$D$2:$D$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Students</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Marks</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Student Marks</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Students'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Students'!$A$2:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Students'!$D$2:$D$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Students</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Marks</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Student Marks - Line Chart</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Students'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Students'!$A$2:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Students'!$D$2:$D$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Students</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Marks</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -388,6 +730,72 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/students.xlsx
+++ b/students.xlsx
@@ -711,6 +711,181 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Student Marks - Line Chart</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Students'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Students'!$A$2:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Students'!$D$2:$D$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Students</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Marks</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Student Marks - Pie Chart</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Students'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Students'!$A$2:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Students'!$D$2:$D$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -796,6 +971,50 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="6" name="Chart 6"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/students.xlsx
+++ b/students.xlsx
@@ -185,6 +185,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FF0000"/>
+          <bgColor rgb="00FF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -886,6 +896,63 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Student Marks - Pie Chart</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Students'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Students'!$A$2:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Students'!$D$2:$D$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -1015,6 +1082,28 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="7" name="Chart 7"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1604,6 +1693,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I16"/>
+  <conditionalFormatting sqref="D2:D16">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>90</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/students.xlsx
+++ b/students.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,34 +30,21 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -69,13 +56,8 @@
         <fgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -99,25 +81,39 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -126,71 +122,66 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin"/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FF0000"/>
-          <bgColor rgb="00FF0000"/>
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00FF00"/>
+          <bgColor rgb="FF00FF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -274,27 +265,35 @@
       <tx>
         <rich>
           <a:bodyPr/>
+          <a:lstStyle/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-IN"/>
               <a:t>Student Marks</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="1"/>
     </title>
     <plotArea>
+      <layout/>
       <barChart>
         <barDir val="col"/>
         <grouping val="clustered"/>
+        <varyColors val="1"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Students'!D1</f>
+              <f>Students!$D$1</f>
+              <strCache>
+                <ptCount val="1"/>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -302,17 +301,75 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="1"/>
           <cat>
-            <numRef>
-              <f>'Students'!$A$2:$A$16</f>
-            </numRef>
+            <strRef>
+              <f>Students!$A$2:$A$16</f>
+              <strCache>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>Nikhitha</v>
+                </pt>
+                <pt idx="1">
+                  <v>Rahul</v>
+                </pt>
+                <pt idx="2">
+                  <v>Priya</v>
+                </pt>
+                <pt idx="3">
+                  <v>Kiran</v>
+                </pt>
+                <pt idx="4">
+                  <v>Anu</v>
+                </pt>
+                <pt idx="5">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="6">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="7">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="8">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="9">
+                  <v>Meena</v>
+                </pt>
+                <pt idx="10">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="11">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="12">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="13">
+                  <v>Meena</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Students'!$D$2:$D$16</f>
+              <f>Students!$D$2:$D$16</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="15"/>
+              </numCache>
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -322,56 +379,243 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="1"/>
+        <axPos val="b"/>
         <title>
           <tx>
             <rich>
               <a:bodyPr/>
+              <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-IN"/>
                   <a:t>Students</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <overlay val="1"/>
         </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="1"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
           <tx>
             <rich>
               <a:bodyPr/>
+              <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-IN"/>
                   <a:t>Marks</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <overlay val="1"/>
         </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
       </valAx>
     </plotArea>
     <legend>
       <legendPos val="r"/>
+      <overlay val="0"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Student Marks - Pie Chart</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="1"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Students!$B$1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Marks</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <strRef>
+              <f>Students!$A$2:$A$15</f>
+              <strCache>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>Nikhitha</v>
+                </pt>
+                <pt idx="1">
+                  <v>Rahul</v>
+                </pt>
+                <pt idx="2">
+                  <v>Priya</v>
+                </pt>
+                <pt idx="3">
+                  <v>Kiran</v>
+                </pt>
+                <pt idx="4">
+                  <v>Anu</v>
+                </pt>
+                <pt idx="5">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="6">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="7">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="8">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="9">
+                  <v>Meena</v>
+                </pt>
+                <pt idx="10">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="11">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="12">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="13">
+                  <v>Meena</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Students!$B$2:$B$15</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>95</v>
+                </pt>
+                <pt idx="1">
+                  <v>85</v>
+                </pt>
+                <pt idx="2">
+                  <v>95</v>
+                </pt>
+                <pt idx="3">
+                  <v>78</v>
+                </pt>
+                <pt idx="4">
+                  <v>88</v>
+                </pt>
+                <pt idx="5">
+                  <v>91</v>
+                </pt>
+                <pt idx="6">
+                  <v>91</v>
+                </pt>
+                <pt idx="7">
+                  <v>87</v>
+                </pt>
+                <pt idx="8">
+                  <v>76</v>
+                </pt>
+                <pt idx="9">
+                  <v>93</v>
+                </pt>
+                <pt idx="10">
+                  <v>91</v>
+                </pt>
+                <pt idx="11">
+                  <v>87</v>
+                </pt>
+                <pt idx="12">
+                  <v>76</v>
+                </pt>
+                <pt idx="13">
+                  <v>93</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+          <showLeaderLines val="1"/>
+        </dLbls>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <overlay val="1"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -386,27 +630,35 @@
       <tx>
         <rich>
           <a:bodyPr/>
+          <a:lstStyle/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-IN"/>
               <a:t>Student Marks</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="1"/>
     </title>
     <plotArea>
+      <layout/>
       <barChart>
         <barDir val="col"/>
         <grouping val="clustered"/>
+        <varyColors val="1"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Students'!D1</f>
+              <f>Students!$D$1</f>
+              <strCache>
+                <ptCount val="1"/>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -414,17 +666,75 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="1"/>
           <cat>
-            <numRef>
-              <f>'Students'!$A$2:$A$16</f>
-            </numRef>
+            <strRef>
+              <f>Students!$A$2:$A$16</f>
+              <strCache>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>Nikhitha</v>
+                </pt>
+                <pt idx="1">
+                  <v>Rahul</v>
+                </pt>
+                <pt idx="2">
+                  <v>Priya</v>
+                </pt>
+                <pt idx="3">
+                  <v>Kiran</v>
+                </pt>
+                <pt idx="4">
+                  <v>Anu</v>
+                </pt>
+                <pt idx="5">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="6">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="7">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="8">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="9">
+                  <v>Meena</v>
+                </pt>
+                <pt idx="10">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="11">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="12">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="13">
+                  <v>Meena</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Students'!$D$2:$D$16</f>
+              <f>Students!$D$2:$D$16</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="15"/>
+              </numCache>
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -434,56 +744,75 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="1"/>
+        <axPos val="b"/>
         <title>
           <tx>
             <rich>
               <a:bodyPr/>
+              <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-IN"/>
                   <a:t>Students</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <overlay val="1"/>
         </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="1"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
           <tx>
             <rich>
               <a:bodyPr/>
+              <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-IN"/>
                   <a:t>Marks</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <overlay val="1"/>
         </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
       </valAx>
     </plotArea>
     <legend>
       <legendPos val="r"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -498,27 +827,35 @@
       <tx>
         <rich>
           <a:bodyPr/>
+          <a:lstStyle/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-IN"/>
               <a:t>Student Marks</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="1"/>
     </title>
     <plotArea>
+      <layout/>
       <barChart>
         <barDir val="col"/>
         <grouping val="clustered"/>
+        <varyColors val="1"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Students'!D1</f>
+              <f>Students!$D$1</f>
+              <strCache>
+                <ptCount val="1"/>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -526,17 +863,75 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="1"/>
           <cat>
-            <numRef>
-              <f>'Students'!$A$2:$A$16</f>
-            </numRef>
+            <strRef>
+              <f>Students!$A$2:$A$16</f>
+              <strCache>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>Nikhitha</v>
+                </pt>
+                <pt idx="1">
+                  <v>Rahul</v>
+                </pt>
+                <pt idx="2">
+                  <v>Priya</v>
+                </pt>
+                <pt idx="3">
+                  <v>Kiran</v>
+                </pt>
+                <pt idx="4">
+                  <v>Anu</v>
+                </pt>
+                <pt idx="5">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="6">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="7">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="8">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="9">
+                  <v>Meena</v>
+                </pt>
+                <pt idx="10">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="11">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="12">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="13">
+                  <v>Meena</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Students'!$D$2:$D$16</f>
+              <f>Students!$D$2:$D$16</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="15"/>
+              </numCache>
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -546,56 +941,75 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="1"/>
+        <axPos val="b"/>
         <title>
           <tx>
             <rich>
               <a:bodyPr/>
+              <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-IN"/>
                   <a:t>Students</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <overlay val="1"/>
         </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="1"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
           <tx>
             <rich>
               <a:bodyPr/>
+              <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-IN"/>
                   <a:t>Marks</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <overlay val="1"/>
         </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
       </valAx>
     </plotArea>
     <legend>
       <legendPos val="r"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -610,26 +1024,34 @@
       <tx>
         <rich>
           <a:bodyPr/>
+          <a:lstStyle/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-IN"/>
               <a:t>Student Marks - Line Chart</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="1"/>
     </title>
     <plotArea>
+      <layout/>
       <lineChart>
         <grouping val="standard"/>
+        <varyColors val="1"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Students'!D1</f>
+              <f>Students!$D$1</f>
+              <strCache>
+                <ptCount val="1"/>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -646,16 +1068,75 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
-              <f>'Students'!$A$2:$A$16</f>
-            </numRef>
+            <strRef>
+              <f>Students!$A$2:$A$16</f>
+              <strCache>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>Nikhitha</v>
+                </pt>
+                <pt idx="1">
+                  <v>Rahul</v>
+                </pt>
+                <pt idx="2">
+                  <v>Priya</v>
+                </pt>
+                <pt idx="3">
+                  <v>Kiran</v>
+                </pt>
+                <pt idx="4">
+                  <v>Anu</v>
+                </pt>
+                <pt idx="5">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="6">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="7">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="8">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="9">
+                  <v>Meena</v>
+                </pt>
+                <pt idx="10">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="11">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="12">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="13">
+                  <v>Meena</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Students'!$D$2:$D$16</f>
+              <f>Students!$D$2:$D$16</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="15"/>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <smooth val="0"/>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -664,56 +1145,75 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="1"/>
+        <axPos val="b"/>
         <title>
           <tx>
             <rich>
               <a:bodyPr/>
+              <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-IN"/>
                   <a:t>Students</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <overlay val="1"/>
         </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="1"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
           <tx>
             <rich>
               <a:bodyPr/>
+              <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-IN"/>
                   <a:t>Marks</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <overlay val="1"/>
         </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
       </valAx>
     </plotArea>
     <legend>
       <legendPos val="r"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -728,26 +1228,34 @@
       <tx>
         <rich>
           <a:bodyPr/>
+          <a:lstStyle/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-IN"/>
               <a:t>Student Marks - Line Chart</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="1"/>
     </title>
     <plotArea>
+      <layout/>
       <lineChart>
         <grouping val="standard"/>
+        <varyColors val="1"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Students'!D1</f>
+              <f>Students!$D$1</f>
+              <strCache>
+                <ptCount val="1"/>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -764,16 +1272,75 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
-              <f>'Students'!$A$2:$A$16</f>
-            </numRef>
+            <strRef>
+              <f>Students!$A$2:$A$16</f>
+              <strCache>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>Nikhitha</v>
+                </pt>
+                <pt idx="1">
+                  <v>Rahul</v>
+                </pt>
+                <pt idx="2">
+                  <v>Priya</v>
+                </pt>
+                <pt idx="3">
+                  <v>Kiran</v>
+                </pt>
+                <pt idx="4">
+                  <v>Anu</v>
+                </pt>
+                <pt idx="5">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="6">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="7">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="8">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="9">
+                  <v>Meena</v>
+                </pt>
+                <pt idx="10">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="11">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="12">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="13">
+                  <v>Meena</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Students'!$D$2:$D$16</f>
+              <f>Students!$D$2:$D$16</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="15"/>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <smooth val="0"/>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -782,56 +1349,75 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="1"/>
+        <axPos val="b"/>
         <title>
           <tx>
             <rich>
               <a:bodyPr/>
+              <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-IN"/>
                   <a:t>Students</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <overlay val="1"/>
         </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="1"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
           <tx>
             <rich>
               <a:bodyPr/>
+              <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-IN"/>
                   <a:t>Marks</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <overlay val="1"/>
         </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
       </valAx>
     </plotArea>
     <legend>
       <legendPos val="r"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -846,18 +1432,22 @@
       <tx>
         <rich>
           <a:bodyPr/>
+          <a:lstStyle/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-IN"/>
               <a:t>Student Marks - Pie Chart</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="1"/>
     </title>
     <plotArea>
+      <layout/>
       <pieChart>
         <varyColors val="1"/>
         <ser>
@@ -865,7 +1455,10 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Students'!D1</f>
+              <f>Students!$D$1</f>
+              <strCache>
+                <ptCount val="1"/>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -874,21 +1467,80 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'Students'!$A$2:$A$16</f>
-            </numRef>
+            <strRef>
+              <f>Students!$A$2:$A$16</f>
+              <strCache>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>Nikhitha</v>
+                </pt>
+                <pt idx="1">
+                  <v>Rahul</v>
+                </pt>
+                <pt idx="2">
+                  <v>Priya</v>
+                </pt>
+                <pt idx="3">
+                  <v>Kiran</v>
+                </pt>
+                <pt idx="4">
+                  <v>Anu</v>
+                </pt>
+                <pt idx="5">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="6">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="7">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="8">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="9">
+                  <v>Meena</v>
+                </pt>
+                <pt idx="10">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="11">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="12">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="13">
+                  <v>Meena</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Students'!$D$2:$D$16</f>
+              <f>Students!$D$2:$D$16</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="15"/>
+              </numCache>
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+          <showLeaderLines val="1"/>
+        </dLbls>
         <firstSliceAng val="0"/>
       </pieChart>
     </plotArea>
     <legend>
       <legendPos val="r"/>
+      <overlay val="1"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -903,18 +1555,22 @@
       <tx>
         <rich>
           <a:bodyPr/>
+          <a:lstStyle/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-IN"/>
               <a:t>Student Marks - Pie Chart</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="1"/>
     </title>
     <plotArea>
+      <layout/>
       <pieChart>
         <varyColors val="1"/>
         <ser>
@@ -922,7 +1578,10 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Students'!D1</f>
+              <f>Students!$D$1</f>
+              <strCache>
+                <ptCount val="1"/>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -931,21 +1590,571 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'Students'!$A$2:$A$16</f>
-            </numRef>
+            <strRef>
+              <f>Students!$A$2:$A$16</f>
+              <strCache>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>Nikhitha</v>
+                </pt>
+                <pt idx="1">
+                  <v>Rahul</v>
+                </pt>
+                <pt idx="2">
+                  <v>Priya</v>
+                </pt>
+                <pt idx="3">
+                  <v>Kiran</v>
+                </pt>
+                <pt idx="4">
+                  <v>Anu</v>
+                </pt>
+                <pt idx="5">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="6">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="7">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="8">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="9">
+                  <v>Meena</v>
+                </pt>
+                <pt idx="10">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="11">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="12">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="13">
+                  <v>Meena</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Students'!$D$2:$D$16</f>
+              <f>Students!$D$2:$D$16</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="15"/>
+              </numCache>
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+          <showLeaderLines val="1"/>
+        </dLbls>
         <firstSliceAng val="0"/>
       </pieChart>
     </plotArea>
     <legend>
       <legendPos val="r"/>
+      <overlay val="1"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Student Marks - Bar Chart</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="1"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Students!$B$1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Marks</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="1"/>
+          <cat>
+            <strRef>
+              <f>Students!$A$2:$A$15</f>
+              <strCache>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>Nikhitha</v>
+                </pt>
+                <pt idx="1">
+                  <v>Rahul</v>
+                </pt>
+                <pt idx="2">
+                  <v>Priya</v>
+                </pt>
+                <pt idx="3">
+                  <v>Kiran</v>
+                </pt>
+                <pt idx="4">
+                  <v>Anu</v>
+                </pt>
+                <pt idx="5">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="6">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="7">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="8">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="9">
+                  <v>Meena</v>
+                </pt>
+                <pt idx="10">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="11">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="12">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="13">
+                  <v>Meena</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Students!$B$2:$B$15</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>95</v>
+                </pt>
+                <pt idx="1">
+                  <v>85</v>
+                </pt>
+                <pt idx="2">
+                  <v>95</v>
+                </pt>
+                <pt idx="3">
+                  <v>78</v>
+                </pt>
+                <pt idx="4">
+                  <v>88</v>
+                </pt>
+                <pt idx="5">
+                  <v>91</v>
+                </pt>
+                <pt idx="6">
+                  <v>91</v>
+                </pt>
+                <pt idx="7">
+                  <v>87</v>
+                </pt>
+                <pt idx="8">
+                  <v>76</v>
+                </pt>
+                <pt idx="9">
+                  <v>93</v>
+                </pt>
+                <pt idx="10">
+                  <v>91</v>
+                </pt>
+                <pt idx="11">
+                  <v>87</v>
+                </pt>
+                <pt idx="12">
+                  <v>76</v>
+                </pt>
+                <pt idx="13">
+                  <v>93</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="b"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN"/>
+                  <a:t>Students</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="1"/>
+        </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN"/>
+                  <a:t>Marks</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="1"/>
+        </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <overlay val="0"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Student Marks - Line Chart</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="1"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <lineChart>
+        <grouping val="standard"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Students!$B$1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Marks</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <strRef>
+              <f>Students!$A$2:$A$15</f>
+              <strCache>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>Nikhitha</v>
+                </pt>
+                <pt idx="1">
+                  <v>Rahul</v>
+                </pt>
+                <pt idx="2">
+                  <v>Priya</v>
+                </pt>
+                <pt idx="3">
+                  <v>Kiran</v>
+                </pt>
+                <pt idx="4">
+                  <v>Anu</v>
+                </pt>
+                <pt idx="5">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="6">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="7">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="8">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="9">
+                  <v>Meena</v>
+                </pt>
+                <pt idx="10">
+                  <v>Ravi</v>
+                </pt>
+                <pt idx="11">
+                  <v>Sita</v>
+                </pt>
+                <pt idx="12">
+                  <v>Arjun</v>
+                </pt>
+                <pt idx="13">
+                  <v>Meena</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Students!$B$2:$B$15</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>95</v>
+                </pt>
+                <pt idx="1">
+                  <v>85</v>
+                </pt>
+                <pt idx="2">
+                  <v>95</v>
+                </pt>
+                <pt idx="3">
+                  <v>78</v>
+                </pt>
+                <pt idx="4">
+                  <v>88</v>
+                </pt>
+                <pt idx="5">
+                  <v>91</v>
+                </pt>
+                <pt idx="6">
+                  <v>91</v>
+                </pt>
+                <pt idx="7">
+                  <v>87</v>
+                </pt>
+                <pt idx="8">
+                  <v>76</v>
+                </pt>
+                <pt idx="9">
+                  <v>93</v>
+                </pt>
+                <pt idx="10">
+                  <v>91</v>
+                </pt>
+                <pt idx="11">
+                  <v>87</v>
+                </pt>
+                <pt idx="12">
+                  <v>76</v>
+                </pt>
+                <pt idx="13">
+                  <v>93</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <smooth val="0"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="b"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN"/>
+                  <a:t>Students</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="1"/>
+        </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN"/>
+                  <a:t>Marks</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="1"/>
+        </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1104,6 +2313,72 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="8" name="Chart 8"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="9" name="Chart 9"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="10" name="Chart 10"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId10"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1401,301 +2676,318 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="3"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="2" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="25.05" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>AGE</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Dynamic Statistics</t>
         </is>
       </c>
+      <c r="G1" s="12" t="n"/>
     </row>
-    <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+    <row r="2" customFormat="1" s="9">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Nikhitha</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="9" t="n">
+      <c r="B2" s="8" t="n">
         <v>95</v>
       </c>
-      <c r="E2" s="9" t="n">
+      <c r="C2" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="H2" s="14" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>Total Marks</t>
         </is>
       </c>
-      <c r="I2" s="9">
-        <f>SUM(D2:D16)</f>
+      <c r="G2" s="8">
+        <f>SUM(B2:B15)</f>
         <v/>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="H3" s="14" t="inlineStr">
+    <row r="3" customFormat="1" s="9">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Average Marks</t>
         </is>
       </c>
-      <c r="I3" s="13">
-        <f>AVERAGE(D2:D16)</f>
+      <c r="G3" s="8">
+        <f>AVERAGE(B2:B15)</f>
         <v/>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+    <row r="4" customFormat="1" s="9">
+      <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>Rahul</t>
+          <t>Priya</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="9" t="n">
-        <v>85</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="B4" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Highest Marks</t>
         </is>
       </c>
-      <c r="I4" s="9">
-        <f>MAX(D2:D16)</f>
+      <c r="G4" s="8">
+        <f>MAX(B2:B15)</f>
         <v/>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+    <row r="5" customFormat="1" s="9">
+      <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Priya</t>
+          <t>Kiran</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="9" t="n">
-        <v>95</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="B5" s="8" t="n">
+        <v>78</v>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Lowest Marks</t>
         </is>
       </c>
-      <c r="I5" s="9">
-        <f>MIN(D2:D16)</f>
+      <c r="G5" s="9">
+        <f>MIN(B2:B15)</f>
         <v/>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Kiran</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="9" t="n">
-        <v>78</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+    <row r="6" customFormat="1" s="9">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Anu</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="9" t="n">
+      <c r="B6" s="8" t="n">
         <v>88</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="C6" s="8" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="7" customFormat="1" s="9">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Ravi</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="9" t="n">
+      <c r="B7" s="8" t="n">
         <v>91</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+    <row r="8" customFormat="1" s="9">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Ravi</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="9" t="n">
+      <c r="B8" s="8" t="n">
         <v>91</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="C8" s="8" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+    <row r="9" customFormat="1" s="9">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sita</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="9" t="n">
+      <c r="B9" s="8" t="n">
         <v>87</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="10" customFormat="1" s="9">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Arjun</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="9" t="n">
+      <c r="B10" s="8" t="n">
         <v>76</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="C10" s="8" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="11" customFormat="1" s="9">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Meena</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="9" t="n">
+      <c r="B11" s="8" t="n">
         <v>93</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="C11" s="8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="12" customFormat="1" s="9">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Ravi</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="9" t="n">
+      <c r="B12" s="8" t="n">
         <v>91</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="C12" s="8" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="13" customFormat="1" s="9">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Sita</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="9" t="n">
+      <c r="B13" s="8" t="n">
         <v>87</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="C13" s="8" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="14" customFormat="1" s="9">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Arjun</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="9" t="n">
+      <c r="B14" s="8" t="n">
         <v>76</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="C14" s="8" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="15" customFormat="1" s="9">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Meena</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="9" t="n">
+      <c r="B15" s="8" t="n">
         <v>93</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="C15" s="8" t="n">
         <v>20</v>
       </c>
     </row>
+    <row r="16" customFormat="1" s="9"/>
+    <row r="17" customFormat="1" s="9"/>
+    <row r="18" customFormat="1" s="9"/>
+    <row r="19" customFormat="1" s="9"/>
+    <row r="20" customFormat="1" s="9"/>
+    <row r="21" customFormat="1" s="9"/>
+    <row r="22" customFormat="1" s="9"/>
+    <row r="23" customFormat="1" s="9"/>
+    <row r="24" customFormat="1" s="9"/>
+    <row r="25" customFormat="1" s="9"/>
+    <row r="26" customFormat="1" s="9"/>
+    <row r="27" customFormat="1" s="9"/>
+    <row r="28" customFormat="1" s="9"/>
+    <row r="29" customFormat="1" s="9"/>
+    <row r="30" customFormat="1" s="9"/>
+    <row r="31" customFormat="1" s="9"/>
+    <row r="32" customFormat="1" s="9"/>
+    <row r="33" customFormat="1" s="9"/>
+    <row r="34" customFormat="1" s="9"/>
+    <row r="35" customFormat="1" s="9"/>
+    <row r="36" customFormat="1" s="9"/>
+    <row r="37" customFormat="1" s="9"/>
+    <row r="38" customFormat="1" s="9"/>
+    <row r="39" customFormat="1" s="9"/>
+    <row r="40" customFormat="1" s="9"/>
+    <row r="41" customFormat="1" s="9"/>
+    <row r="42" customFormat="1" s="9"/>
+    <row r="43" customFormat="1" s="9"/>
+    <row r="44" customFormat="1" s="9"/>
+    <row r="45" customFormat="1" s="9"/>
+    <row r="46" customFormat="1" s="9"/>
+    <row r="47" customFormat="1" s="9"/>
+    <row r="48" customFormat="1" s="9"/>
+    <row r="49" customFormat="1" s="9"/>
+    <row r="50" customFormat="1" s="9"/>
+    <row r="51" customFormat="1" s="9"/>
+    <row r="52" customFormat="1" s="9"/>
+    <row r="53" customFormat="1" s="9"/>
+    <row r="54" customFormat="1" s="9"/>
+    <row r="55" customFormat="1" s="9"/>
+    <row r="56" customFormat="1" s="9"/>
+    <row r="57" customFormat="1" s="9"/>
+    <row r="58" customFormat="1" s="9"/>
+    <row r="59" customFormat="1" s="9"/>
   </sheetData>
   <autoFilter ref="A1:I16"/>
-  <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+  <conditionalFormatting sqref="B2:B15">
+    <cfRule type="cellIs" priority="4" operator="greaterThan" dxfId="1">
       <formula>90</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="0">
+      <formula>80</formula>
+    </cfRule>
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1717,50 +3009,50 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Student Summary</t>
         </is>
       </c>
-      <c r="B1" s="11" t="n"/>
+      <c r="B1" s="7" t="n"/>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+    <row r="2" ht="22.05" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Total Students</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="1" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+    <row r="3" ht="22.05" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Average Marks</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n">
+      <c r="B3" s="3" t="n">
         <v>87.57142857142857</v>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+    <row r="4" ht="22.05" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Highest Marks</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="1" t="n">
         <v>95</v>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+    <row r="5" ht="22.05" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Lowest Marks</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="1" t="n">
         <v>76</v>
       </c>
     </row>
